--- a/forms/trg/Formulir_TRG_supplychain-m.xlsx
+++ b/forms/trg/Formulir_TRG_supplychain-m.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B23)</f>
+        <f>COUNTA(Anggota!B5:B24)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F23)</f>
+        <f>COUNTA(Anggota!F5:F24)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Associate Professor. Dr. Sabbar Dahham Sabbar</t>
+          <t>Prof. Dr. Maat Pono, SE., M.Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Economics</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Islamic Economics and Business</t>
+          <t>Operational Management</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +933,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-8317-8458</t>
+          <t>0000-0002-8906-8743</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6863841</t>
+          <t>6026655</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>58155587300</t>
+          <t>57191665786</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Musran Munizu, S.E., M.Si</t>
+          <t>Associate Professor. Dr. Sabbar Dahham Sabbar</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Supply Chain Management</t>
+          <t>Islamic Economics and Business</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -986,17 +982,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9687-3441</t>
+          <t>0000-0002-8317-8458</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>5976956</t>
+          <t>6863841</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57195626627</t>
+          <t>58155587300</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,22 +1007,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Mohamed Ibrid Mugableh</t>
+          <t>Prof. Dr. Musran Munizu, S.E., M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Irbid National University</t>
+          <t>Faculty of Economics</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Finance Management and Bancking</t>
+          <t>Supply Chain Management</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1035,13 +1031,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3974-8185</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="n"/>
+          <t>0000-0002-9687-3441</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>5976956</t>
+        </is>
+      </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57188658995</t>
+          <t>57195626627</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1056,27 +1056,39 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>M. Iqbal</t>
+          <t>Prof. Mohamed Ibrid Mugableh</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Irbid National University</t>
+        </is>
+      </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Operations Management</t>
+          <t>Finance Management and Bancking</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-3974-8185</t>
+        </is>
+      </c>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>57188658995</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1089,22 +1101,18 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Marissa Siloy</t>
+          <t>M. Iqbal</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Economics</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Finance and Banking</t>
+          <t>Operations Management</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1112,11 +1120,7 @@
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>6098951</t>
-        </is>
-      </c>
+      <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
@@ -1130,22 +1134,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Nurhaya Yusuf</t>
+          <t>Marissa Siloy</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Faculty of Economics</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Development of Local Industries and Community-Based Enterprises</t>
+          <t>Finance and Banking</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1155,14 +1159,10 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6111116</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>57211312150</t>
-        </is>
-      </c>
+          <t>6098951</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Hariyanti</t>
+          <t>Nurhaya Yusuf</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1190,24 +1190,24 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Green Financing and Enterprise</t>
+          <t>Development of Local Industries and Community-Based Enterprises</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0009-0000-3132-5578</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>6683959</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="n"/>
+          <t>6111116</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>57211312150</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1218,18 +1218,46 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Hariyanti</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Green Financing and Enterprise</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0009-0000-3132-5578</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
+        <is>
+          <t>6683959</t>
+        </is>
+      </c>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1418,15 +1446,32 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
